--- a/预测水位/OutputData/水地1(out).xlsx
+++ b/预测水位/OutputData/水地1(out).xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2161"/>
+  <dimension ref="A1:B2185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17723,7 +17723,199 @@
         <v>45837.91666666666</v>
       </c>
       <c r="B2161" t="n">
-        <v>887.452</v>
+        <v>887.4</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B2162" t="n">
+        <v>887.348</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="2" t="n">
+        <v>45838.08333333334</v>
+      </c>
+      <c r="B2163" t="n">
+        <v>887.3175</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="2" t="n">
+        <v>45838.16666666666</v>
+      </c>
+      <c r="B2164" t="n">
+        <v>887.287</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="2" t="n">
+        <v>45838.25</v>
+      </c>
+      <c r="B2165" t="n">
+        <v>887.2615000000001</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="2" t="n">
+        <v>45838.33333333334</v>
+      </c>
+      <c r="B2166" t="n">
+        <v>887.236</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="2" t="n">
+        <v>45838.41666666666</v>
+      </c>
+      <c r="B2167" t="n">
+        <v>887.1994999999999</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="2" t="n">
+        <v>45838.5</v>
+      </c>
+      <c r="B2168" t="n">
+        <v>887.163</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="2" t="n">
+        <v>45838.58333333334</v>
+      </c>
+      <c r="B2169" t="n">
+        <v>887.1385</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="2" t="n">
+        <v>45838.66666666666</v>
+      </c>
+      <c r="B2170" t="n">
+        <v>887.114</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="2" t="n">
+        <v>45838.75</v>
+      </c>
+      <c r="B2171" t="n">
+        <v>887.079</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="2" t="n">
+        <v>45838.83333333334</v>
+      </c>
+      <c r="B2172" t="n">
+        <v>887.044</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="2" t="n">
+        <v>45838.91666666666</v>
+      </c>
+      <c r="B2173" t="n">
+        <v>887.0155</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B2174" t="n">
+        <v>886.987</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="2" t="n">
+        <v>45839.08333333334</v>
+      </c>
+      <c r="B2175" t="n">
+        <v>886.979</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="2" t="n">
+        <v>45839.16666666666</v>
+      </c>
+      <c r="B2176" t="n">
+        <v>886.971</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="2" t="n">
+        <v>45839.25</v>
+      </c>
+      <c r="B2177" t="n">
+        <v>886.953</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="2" t="n">
+        <v>45839.33333333334</v>
+      </c>
+      <c r="B2178" t="n">
+        <v>886.9349999999999</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="2" t="n">
+        <v>45839.41666666666</v>
+      </c>
+      <c r="B2179" t="n">
+        <v>886.9245</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="2" t="n">
+        <v>45839.5</v>
+      </c>
+      <c r="B2180" t="n">
+        <v>886.914</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="2" t="n">
+        <v>45839.58333333334</v>
+      </c>
+      <c r="B2181" t="n">
+        <v>886.9025</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="2" t="n">
+        <v>45839.66666666666</v>
+      </c>
+      <c r="B2182" t="n">
+        <v>886.891</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="2" t="n">
+        <v>45839.75</v>
+      </c>
+      <c r="B2183" t="n">
+        <v>886.873</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="2" t="n">
+        <v>45839.83333333334</v>
+      </c>
+      <c r="B2184" t="n">
+        <v>886.855</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="2" t="n">
+        <v>45839.91666666666</v>
+      </c>
+      <c r="B2185" t="n">
+        <v>886.855</v>
       </c>
     </row>
   </sheetData>
